--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124152641</v>
+        <v>124155454</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447136</v>
+        <v>447140</v>
       </c>
       <c r="R2" t="n">
-        <v>6540822</v>
+        <v>6540857</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,11 +778,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124155454</v>
+        <v>124152641</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -840,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447140</v>
+        <v>447136</v>
       </c>
       <c r="R3" t="n">
-        <v>6540857</v>
+        <v>6540822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +883,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +903,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124155454</v>
+        <v>124153007</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447140</v>
+        <v>447138</v>
       </c>
       <c r="R3" t="n">
-        <v>6540857</v>
+        <v>6540807</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +893,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +913,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124153007</v>
+        <v>124155454</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447138</v>
+        <v>447140</v>
       </c>
       <c r="R4" t="n">
-        <v>6540807</v>
+        <v>6540857</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,11 +1023,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,11 +1038,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124153007</v>
+        <v>124155454</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447138</v>
+        <v>447140</v>
       </c>
       <c r="R3" t="n">
-        <v>6540807</v>
+        <v>6540857</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,11 +893,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,11 +908,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124155454</v>
+        <v>124153007</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -970,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447140</v>
+        <v>447138</v>
       </c>
       <c r="R4" t="n">
-        <v>6540857</v>
+        <v>6540807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,6 +1013,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +1033,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124152641</v>
+        <v>124153007</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447136</v>
+        <v>447138</v>
       </c>
       <c r="R2" t="n">
-        <v>6540822</v>
+        <v>6540807</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124155454</v>
+        <v>124152641</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447140</v>
+        <v>447136</v>
       </c>
       <c r="R3" t="n">
-        <v>6540857</v>
+        <v>6540822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +893,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +913,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124153007</v>
+        <v>124155454</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447138</v>
+        <v>447140</v>
       </c>
       <c r="R4" t="n">
-        <v>6540807</v>
+        <v>6540857</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,11 +1023,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,11 +1038,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124153007</v>
+        <v>124155454</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447138</v>
+        <v>447140</v>
       </c>
       <c r="R2" t="n">
-        <v>6540807</v>
+        <v>6540857</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,11 +778,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -935,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124155454</v>
+        <v>124153007</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -970,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447140</v>
+        <v>447138</v>
       </c>
       <c r="R4" t="n">
-        <v>6540857</v>
+        <v>6540807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,6 +1013,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +1033,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124155454</v>
+        <v>124153007</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447140</v>
+        <v>447138</v>
       </c>
       <c r="R2" t="n">
-        <v>6540857</v>
+        <v>6540807</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +783,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124152641</v>
+        <v>124155454</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -830,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -847,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447136</v>
+        <v>447140</v>
       </c>
       <c r="R3" t="n">
-        <v>6540822</v>
+        <v>6540857</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,11 +893,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,11 +908,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124153007</v>
+        <v>124152641</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447138</v>
+        <v>447136</v>
       </c>
       <c r="R4" t="n">
-        <v>6540807</v>
+        <v>6540822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124153007</v>
+        <v>124152641</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447138</v>
+        <v>447136</v>
       </c>
       <c r="R2" t="n">
-        <v>6540807</v>
+        <v>6540822</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124155454</v>
+        <v>124153007</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447140</v>
+        <v>447138</v>
       </c>
       <c r="R3" t="n">
-        <v>6540857</v>
+        <v>6540807</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +893,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +913,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124152641</v>
+        <v>124155454</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447136</v>
+        <v>447140</v>
       </c>
       <c r="R4" t="n">
-        <v>6540822</v>
+        <v>6540857</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,11 +1023,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,11 +1038,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124152641</v>
+        <v>124153007</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447136</v>
+        <v>447138</v>
       </c>
       <c r="R2" t="n">
-        <v>6540822</v>
+        <v>6540807</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124153007</v>
+        <v>124152641</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m O om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447138</v>
+        <v>447136</v>
       </c>
       <c r="R3" t="n">
-        <v>6540807</v>
+        <v>6540822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 12709-2025 artfynd.xlsx
+++ b/artfynd/A 12709-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124153007</v>
+        <v>98842996</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MYSTEN 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m Ö om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447138</v>
+        <v>447159</v>
       </c>
       <c r="R2" t="n">
-        <v>6540807</v>
+        <v>6540850</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
+          <t>Fastighet Gullspång Nunnestad 1:21 (5). Äldre talldominerad skog.  Ca 10 m Ö om Mystenvägen, 2 m SV om skadad gran (diagonal "reva" i barken i brösthöjd), nedanför (N om)  stor sten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,16 +774,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124152641</v>
+        <v>98843396</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,17 +833,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m Ö om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447136</v>
+        <v>447162</v>
       </c>
       <c r="R3" t="n">
-        <v>6540822</v>
+        <v>6540850</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,17 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
+          <t>Ca 13 m Ö om Mystenvägen. Fastighet Gullspång Nunnestad 1:21 (5). Äldre talldominerad skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,16 +889,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -935,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124155454</v>
+        <v>98843457</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,17 +948,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MYSTEN, 100 m O om, Vg</t>
+          <t>MYSTEN, 100 m Ö om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447140</v>
+        <v>447165</v>
       </c>
       <c r="R4" t="n">
-        <v>6540857</v>
+        <v>6540850</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,12 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 15 m Ö om Mystenvägen. Fastighet Gullspång Nunnestad 1:21 (5). Äldre talldominerad skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,11 +1005,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1052,6 +1017,601 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98844072</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>MYSTEN, 100 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>447162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6540883</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre talldominerad skog med tjocka mossbäddar. Ca 5 m Ö om grusväg.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98844100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MYSTEN, 100 m Ö om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>447158</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6540877</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 blomstängel. Ca 10 m Ö om Mystenvägen. Telefonledning 10 m S om.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124152641</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>MYSTEN, 100 m O om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>447136</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6540822</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124153007</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MYSTEN 100 m O om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>447138</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540807</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barrblandskog med naturskogskvaliteter. Flerskiktad, med äldre tallar som överståndare. Tjocka mossbäddar, flerstädes. Inslag av stående död ved av tall, och liggande död ved av gran. Marken svagt sluttande mot V.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Flerskiktad. Äldre tall som överståndare. Inslag av gran, ek, björk, rönn. I fältskiktet mestadels blåbärsris. Inslag av frylen, enstaka linnea. Tjocka mossbäddar av husmossa. Stående död ved förekommer: torrfuror (tall) – samt liggande död ved av gran.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124155454</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>MYSTEN, 100 m O om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>447140</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540857</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Amnehärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johanna Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
